--- a/output/2026-10-07/enriched_analysis.xlsx
+++ b/output/2026-10-07/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.188</v>
+        <v>2.062</v>
       </c>
       <c r="W2" t="n">
-        <v>2880</v>
+        <v>3056</v>
       </c>
       <c r="X2" t="n">
-        <v>22.6</v>
+        <v>23.9</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.843</v>
+        <v>0.845</v>
       </c>
       <c r="W3" t="n">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="X3" t="n">
         <v>134</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="W4" t="n">
-        <v>2765</v>
+        <v>2836</v>
       </c>
       <c r="X4" t="n">
-        <v>9.5</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Y4" t="n">
         <v>36</v>
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>1.162</v>
+        <v>1.166</v>
       </c>
       <c r="W5" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="X5" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Y5" t="n">
         <v>22</v>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.707</v>
+        <v>1.742</v>
       </c>
       <c r="W6" t="n">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.325</v>
+        <v>0.323</v>
       </c>
       <c r="W7" t="n">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="X7" t="n">
-        <v>9.26</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y7" t="n">
         <v>7</v>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.53</v>
+        <v>0.537</v>
       </c>
       <c r="W8" t="n">
-        <v>2696</v>
+        <v>2660</v>
       </c>
       <c r="X8" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="Y8" t="n">
         <v>8</v>
@@ -2557,7 +2557,7 @@
         <v>185</v>
       </c>
       <c r="X9" t="n">
-        <v>7.86</v>
+        <v>7.87</v>
       </c>
       <c r="Y9" t="n">
         <v>17</v>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="W10" t="n">
-        <v>14790</v>
+        <v>15093</v>
       </c>
       <c r="X10" t="n">
-        <v>37.7</v>
+        <v>38.5</v>
       </c>
       <c r="Y10" t="n">
         <v>83</v>
@@ -3018,7 +3018,7 @@
         <v>0.126</v>
       </c>
       <c r="W11" t="n">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="X11" t="n">
         <v>21.8</v>
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2.254</v>
+        <v>2.261</v>
       </c>
       <c r="W12" t="n">
-        <v>2604</v>
+        <v>2596</v>
       </c>
       <c r="X12" t="n">
         <v>204</v>
@@ -3482,10 +3482,10 @@
         <v>0.048</v>
       </c>
       <c r="W13" t="n">
-        <v>1718</v>
+        <v>1704</v>
       </c>
       <c r="X13" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="Y13" t="n">
         <v>55</v>
@@ -3711,13 +3711,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.065</v>
+        <v>0.066</v>
       </c>
       <c r="W14" t="n">
-        <v>874</v>
+        <v>862</v>
       </c>
       <c r="X14" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="Y14" t="n">
         <v>19</v>
@@ -3941,13 +3941,13 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>2.714</v>
+        <v>2.783</v>
       </c>
       <c r="W15" t="n">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="X15" t="n">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="Y15" t="n">
         <v>30</v>
@@ -4167,13 +4167,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
       <c r="W16" t="n">
-        <v>1746</v>
+        <v>1727</v>
       </c>
       <c r="X16" t="n">
-        <v>40.1</v>
+        <v>39.7</v>
       </c>
       <c r="Y16" t="n">
         <v>20</v>
@@ -4399,13 +4399,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.123</v>
+        <v>0.12</v>
       </c>
       <c r="W17" t="n">
-        <v>700</v>
+        <v>716</v>
       </c>
       <c r="X17" t="n">
-        <v>30.5</v>
+        <v>31.2</v>
       </c>
       <c r="Y17" t="n">
         <v>17</v>
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>1.814</v>
+        <v>1.845</v>
       </c>
       <c r="W18" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="n">
@@ -4858,10 +4858,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>55099</v>
+        <v>54470</v>
       </c>
       <c r="X19" t="n">
-        <v>46.7</v>
+        <v>46.2</v>
       </c>
       <c r="Y19" t="n">
         <v>5</v>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.185</v>
+        <v>0.179</v>
       </c>
       <c r="W20" t="n">
-        <v>600</v>
+        <v>619</v>
       </c>
       <c r="X20" t="n">
-        <v>50.1</v>
+        <v>51.7</v>
       </c>
       <c r="Y20" t="n">
         <v>3</v>
@@ -5319,13 +5319,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="W21" t="n">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="X21" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="Y21" t="n">
         <v>-5</v>
@@ -5551,13 +5551,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
       <c r="W22" t="n">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="X22" t="n">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
       <c r="Y22" t="n">
         <v>21</v>
@@ -5783,13 +5783,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.663</v>
+        <v>0.679</v>
       </c>
       <c r="W23" t="n">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="X23" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="Y23" t="n">
         <v>19</v>
@@ -6015,13 +6015,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>1.033</v>
+        <v>1.012</v>
       </c>
       <c r="W24" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="X24" t="n">
-        <v>5.63</v>
+        <v>5.73</v>
       </c>
       <c r="Y24" t="n">
         <v>31</v>
@@ -6243,13 +6243,13 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.328</v>
+        <v>0.347</v>
       </c>
       <c r="W25" t="n">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="X25" t="n">
-        <v>23.4</v>
+        <v>22.1</v>
       </c>
       <c r="Y25" t="n">
         <v>12</v>
@@ -6475,13 +6475,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.513</v>
+        <v>0.52</v>
       </c>
       <c r="W26" t="n">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="X26" t="n">
-        <v>36.1</v>
+        <v>35.7</v>
       </c>
       <c r="Y26" t="n">
         <v>21</v>
@@ -6707,13 +6707,13 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.519</v>
+        <v>0.516</v>
       </c>
       <c r="W27" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="X27" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="Y27" t="n">
         <v>-44</v>
@@ -6939,13 +6939,13 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.136</v>
+        <v>0.125</v>
       </c>
       <c r="W28" t="n">
-        <v>588</v>
+        <v>641</v>
       </c>
       <c r="X28" t="n">
-        <v>13</v>
+        <v>14.1</v>
       </c>
       <c r="Y28" t="n">
         <v>-1</v>
@@ -7171,13 +7171,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.237</v>
+        <v>0.235</v>
       </c>
       <c r="W29" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="X29" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="Y29" t="n">
         <v>16</v>
@@ -7406,7 +7406,7 @@
         <v>0.043</v>
       </c>
       <c r="W30" t="n">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="X30" t="n">
         <v>20.9</v>
@@ -7861,13 +7861,13 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.829</v>
+        <v>0.819</v>
       </c>
       <c r="W32" t="n">
-        <v>3810</v>
+        <v>3856</v>
       </c>
       <c r="X32" t="n">
-        <v>26.7</v>
+        <v>27</v>
       </c>
       <c r="Y32" t="n">
         <v>2</v>
@@ -8093,13 +8093,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.291</v>
+        <v>0.283</v>
       </c>
       <c r="W33" t="n">
-        <v>895</v>
+        <v>919</v>
       </c>
       <c r="X33" t="n">
-        <v>24.4</v>
+        <v>25</v>
       </c>
       <c r="Y33" t="n">
         <v>9</v>
@@ -8325,13 +8325,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.663</v>
+        <v>0.671</v>
       </c>
       <c r="W34" t="n">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="X34" t="n">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="Y34" t="n">
         <v>-61</v>
@@ -8559,7 +8559,7 @@
         <v>384</v>
       </c>
       <c r="X35" t="n">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="Y35" t="n">
         <v>246</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.226</v>
+        <v>0.228</v>
       </c>
       <c r="W36" t="n">
-        <v>1766</v>
+        <v>1752</v>
       </c>
       <c r="X36" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="Y36" t="n">
         <v>-3</v>
@@ -9020,10 +9020,10 @@
         <v>0.041</v>
       </c>
       <c r="W37" t="n">
-        <v>3257</v>
+        <v>3275</v>
       </c>
       <c r="X37" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="Y37" t="n">
         <v>-4</v>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>5317</v>
+        <v>5418</v>
       </c>
       <c r="X38" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="Y38" t="n">
         <v>26</v>
@@ -9484,7 +9484,7 @@
         <v>0.011</v>
       </c>
       <c r="W39" t="n">
-        <v>4183</v>
+        <v>4155</v>
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
@@ -9714,10 +9714,10 @@
         <v>0.114</v>
       </c>
       <c r="W40" t="n">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="X40" t="n">
-        <v>7.05</v>
+        <v>7.03</v>
       </c>
       <c r="Y40" t="n">
         <v>118</v>
@@ -10171,13 +10171,13 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.131</v>
+        <v>0.138</v>
       </c>
       <c r="W42" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="X42" t="n">
-        <v>35.5</v>
+        <v>33.8</v>
       </c>
       <c r="Y42" t="n">
         <v>19</v>
@@ -10403,13 +10403,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="W43" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X43" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="Y43" t="n">
         <v>24</v>
@@ -10635,10 +10635,10 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="W44" t="n">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
@@ -10868,10 +10868,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3830</v>
+        <v>3902</v>
       </c>
       <c r="X45" t="n">
-        <v>86.2</v>
+        <v>87.8</v>
       </c>
       <c r="Y45" t="n">
         <v>42</v>
@@ -11100,10 +11100,10 @@
         <v>0.006</v>
       </c>
       <c r="W46" t="n">
-        <v>4843</v>
+        <v>4898</v>
       </c>
       <c r="X46" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="Y46" t="n">
         <v>23</v>
@@ -11328,10 +11328,10 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>110771</v>
+        <v>108435</v>
       </c>
       <c r="X47" t="n">
-        <v>31.9</v>
+        <v>31.2</v>
       </c>
       <c r="Y47" t="n">
         <v>18</v>
@@ -11557,13 +11557,13 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>0.218</v>
+        <v>0.217</v>
       </c>
       <c r="W48" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="X48" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Y48" t="n">
         <v>21</v>

--- a/output/2026-10-07/enriched_analysis.xlsx
+++ b/output/2026-10-07/enriched_analysis.xlsx
@@ -886,13 +886,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>86.67</v>
+        <v>91.75</v>
       </c>
       <c r="J2" t="n">
         <v>77.33</v>
       </c>
       <c r="K2" t="n">
-        <v>12.1</v>
+        <v>18.6</v>
       </c>
       <c r="L2" t="n">
         <v>61.32</v>
@@ -932,7 +932,7 @@
         <v>2.062</v>
       </c>
       <c r="W2" t="n">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="X2" t="n">
         <v>23.9</v>
@@ -962,19 +962,19 @@
         <v>6</v>
       </c>
       <c r="AG2" t="n">
-        <v>81.77</v>
+        <v>81.98</v>
       </c>
       <c r="AH2" t="n">
-        <v>57.96</v>
+        <v>58.25</v>
       </c>
       <c r="AI2" t="n">
-        <v>65.40000000000001</v>
+        <v>59.2</v>
       </c>
       <c r="AJ2" t="n">
         <v>77.33020135925074</v>
       </c>
       <c r="AK2" t="n">
-        <v>12.1</v>
+        <v>18.6</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1118,13 +1118,13 @@
         <v>-1</v>
       </c>
       <c r="I3" t="n">
-        <v>835.6</v>
+        <v>824.9</v>
       </c>
       <c r="J3" t="n">
         <v>819.08</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="L3" t="n">
         <v>73</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.845</v>
+        <v>0.854</v>
       </c>
       <c r="W3" t="n">
-        <v>958</v>
+        <v>948</v>
       </c>
       <c r="X3" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Y3" t="n">
         <v>47</v>
@@ -1194,19 +1194,19 @@
         <v>25.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>786.03</v>
+        <v>787.37</v>
       </c>
       <c r="AH3" t="n">
-        <v>669.3099999999999</v>
+        <v>669.8099999999999</v>
       </c>
       <c r="AI3" t="n">
-        <v>65.40000000000001</v>
+        <v>58.9</v>
       </c>
       <c r="AJ3" t="n">
         <v>819.0814633455414</v>
       </c>
       <c r="AK3" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1350,13 +1350,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>282.5</v>
+        <v>299.2</v>
       </c>
       <c r="J4" t="n">
         <v>265.56</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>12.7</v>
       </c>
       <c r="L4" t="n">
         <v>64.63</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
       <c r="W4" t="n">
-        <v>2836</v>
+        <v>2926</v>
       </c>
       <c r="X4" t="n">
-        <v>9.779999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="Y4" t="n">
         <v>36</v>
@@ -1426,19 +1426,19 @@
         <v>16</v>
       </c>
       <c r="AG4" t="n">
-        <v>255.89</v>
+        <v>256.96</v>
       </c>
       <c r="AH4" t="n">
-        <v>180.77</v>
+        <v>181.64</v>
       </c>
       <c r="AI4" t="n">
-        <v>123.3</v>
+        <v>134.2</v>
       </c>
       <c r="AJ4" t="n">
         <v>265.56012</v>
       </c>
       <c r="AK4" t="n">
-        <v>6.4</v>
+        <v>12.7</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1553,12 +1553,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1573,37 +1573,37 @@
         <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>338.55</v>
+        <v>944.4</v>
       </c>
       <c r="J5" t="n">
-        <v>333.11</v>
+        <v>869.9299999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="L5" t="n">
-        <v>63.24</v>
+        <v>61.71</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>5.19</v>
       </c>
       <c r="N5" t="n">
-        <v>37538354</v>
+        <v>51906767</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>37538354</v>
+        <v>51906767</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1625,52 +1625,50 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>1.166</v>
+        <v>1.778</v>
       </c>
       <c r="W5" t="n">
-        <v>322</v>
-      </c>
-      <c r="X5" t="n">
-        <v>148</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.45</v>
+        <v>11.91</v>
       </c>
       <c r="AA5" t="n">
-        <v>264</v>
+        <v>-184</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.55</v>
+        <v>31.98</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.07</v>
+        <v>-0.26</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>6.06</v>
+        <v>57.93</v>
       </c>
       <c r="AG5" t="n">
-        <v>332.64</v>
+        <v>838.65</v>
       </c>
       <c r="AH5" t="n">
-        <v>283.68</v>
+        <v>792.4400000000001</v>
       </c>
       <c r="AI5" t="n">
-        <v>42.4</v>
+        <v>17.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>333.1146252074293</v>
+        <v>869.9263759469062</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -1689,7 +1687,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1698,10 +1696,10 @@
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="AR5" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="AS5" t="n">
         <v>7</v>
@@ -1710,31 +1708,31 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10185611</v>
+        <v>23141272</v>
       </c>
       <c r="BA5" t="n">
-        <v>20160466</v>
+        <v>30615178</v>
       </c>
       <c r="BB5" t="n">
-        <v>23414636</v>
+        <v>51906767</v>
       </c>
       <c r="BC5" t="n">
-        <v>37538354</v>
+        <v>51906767</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
@@ -1770,10 +1768,10 @@
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>20160466</v>
+        <v>30615178</v>
       </c>
       <c r="BP5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
@@ -1785,16 +1783,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1805,37 +1803,37 @@
         <v>18</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I6" t="n">
-        <v>983.2</v>
+        <v>333.9</v>
       </c>
       <c r="J6" t="n">
-        <v>869.9299999999999</v>
+        <v>333.11</v>
       </c>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>0.2</v>
       </c>
       <c r="L6" t="n">
-        <v>61.71</v>
+        <v>63.24</v>
       </c>
       <c r="M6" t="n">
-        <v>5.19</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>51906767</v>
+        <v>37538354</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>51906767</v>
+        <v>37538354</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1849,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1857,50 +1855,52 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.742</v>
+        <v>1.195</v>
       </c>
       <c r="W6" t="n">
-        <v>298</v>
-      </c>
-      <c r="X6" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="X6" t="n">
+        <v>145</v>
+      </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.91</v>
+        <v>2.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>-184</v>
+        <v>264</v>
       </c>
       <c r="AB6" t="n">
-        <v>31.98</v>
+        <v>2.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.26</v>
+        <v>2.07</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>57.93</v>
+        <v>6.06</v>
       </c>
       <c r="AG6" t="n">
-        <v>833.3099999999999</v>
+        <v>333</v>
       </c>
       <c r="AH6" t="n">
-        <v>791.51</v>
+        <v>283.87</v>
       </c>
       <c r="AI6" t="n">
-        <v>22.1</v>
+        <v>38.6</v>
       </c>
       <c r="AJ6" t="n">
-        <v>869.9263759469062</v>
+        <v>333.1146252074293</v>
       </c>
       <c r="AK6" t="n">
-        <v>13</v>
+        <v>0.2</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AR6" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="AS6" t="n">
         <v>7</v>
@@ -1940,70 +1940,70 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>10185611</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>20160466</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>23414636</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>37538354</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>20160466</v>
+      </c>
+      <c r="BP6" t="n">
         <v>3</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>23141272</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>30615178</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>51906767</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>51906767</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>30615178</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
@@ -2044,13 +2044,13 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>548.65</v>
+        <v>549.15</v>
       </c>
       <c r="J7" t="n">
         <v>510.94</v>
       </c>
       <c r="K7" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="L7" t="n">
         <v>62.09</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.323</v>
+        <v>0.325</v>
       </c>
       <c r="W7" t="n">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="X7" t="n">
-        <v>9.300000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="Y7" t="n">
         <v>7</v>
@@ -2120,19 +2120,19 @@
         <v>14</v>
       </c>
       <c r="AG7" t="n">
-        <v>515.0599999999999</v>
+        <v>516.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>491.95</v>
+        <v>492.24</v>
       </c>
       <c r="AI7" t="n">
-        <v>30.2</v>
+        <v>29.1</v>
       </c>
       <c r="AJ7" t="n">
         <v>510.9380308010612</v>
       </c>
       <c r="AK7" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -2276,13 +2276,13 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>104.99</v>
+        <v>103.57</v>
       </c>
       <c r="J8" t="n">
         <v>96.81999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
         <v>70.88</v>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.537</v>
+        <v>0.538</v>
       </c>
       <c r="W8" t="n">
-        <v>2660</v>
+        <v>2654</v>
       </c>
       <c r="X8" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Y8" t="n">
         <v>8</v>
@@ -2352,19 +2352,19 @@
         <v>30</v>
       </c>
       <c r="AG8" t="n">
-        <v>97.59</v>
+        <v>97.86</v>
       </c>
       <c r="AH8" t="n">
         <v>92.64</v>
       </c>
       <c r="AI8" t="n">
-        <v>34.8</v>
+        <v>28.8</v>
       </c>
       <c r="AJ8" t="n">
         <v>96.81860858409144</v>
       </c>
       <c r="AK8" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -2508,13 +2508,13 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>62.86</v>
+        <v>61.19</v>
       </c>
       <c r="J9" t="n">
         <v>74.22</v>
       </c>
       <c r="K9" t="n">
-        <v>-15.3</v>
+        <v>-17.6</v>
       </c>
       <c r="L9" t="n">
         <v>72.56999999999999</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>1.085</v>
+        <v>1.127</v>
       </c>
       <c r="W9" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="X9" t="n">
-        <v>7.87</v>
+        <v>7.57</v>
       </c>
       <c r="Y9" t="n">
         <v>17</v>
@@ -2584,19 +2584,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>66.76000000000001</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="AH9" t="n">
-        <v>53.35</v>
+        <v>53.38</v>
       </c>
       <c r="AI9" t="n">
-        <v>34.4</v>
+        <v>29.6</v>
       </c>
       <c r="AJ9" t="n">
         <v>74.21830535305453</v>
       </c>
       <c r="AK9" t="n">
-        <v>-15.3</v>
+        <v>-17.6</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
@@ -2740,13 +2740,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4758.5</v>
+        <v>4803</v>
       </c>
       <c r="J10" t="n">
         <v>5198.76</v>
       </c>
       <c r="K10" t="n">
-        <v>-8.5</v>
+        <v>-7.6</v>
       </c>
       <c r="L10" t="n">
         <v>67.16</v>
@@ -2786,10 +2786,10 @@
         <v>0.048</v>
       </c>
       <c r="W10" t="n">
-        <v>15093</v>
+        <v>14926</v>
       </c>
       <c r="X10" t="n">
-        <v>38.5</v>
+        <v>38</v>
       </c>
       <c r="Y10" t="n">
         <v>83</v>
@@ -2816,19 +2816,19 @@
         <v>5</v>
       </c>
       <c r="AG10" t="n">
-        <v>5318.36</v>
+        <v>5268.23</v>
       </c>
       <c r="AH10" t="n">
-        <v>4508.46</v>
+        <v>4516.49</v>
       </c>
       <c r="AI10" t="n">
-        <v>34.3</v>
+        <v>28</v>
       </c>
       <c r="AJ10" t="n">
         <v>5198.755988455989</v>
       </c>
       <c r="AK10" t="n">
-        <v>-8.5</v>
+        <v>-7.6</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
@@ -2972,13 +2972,13 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>95.09999999999999</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="J11" t="n">
         <v>75.68000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>25.7</v>
+        <v>26.8</v>
       </c>
       <c r="L11" t="n">
         <v>74.84999999999999</v>
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.126</v>
+        <v>0.125</v>
       </c>
       <c r="W11" t="n">
-        <v>2484</v>
+        <v>2510</v>
       </c>
       <c r="X11" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
         <v>-3</v>
@@ -3048,19 +3048,19 @@
         <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>73.19</v>
+        <v>74.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>49.19</v>
+        <v>49.43</v>
       </c>
       <c r="AI11" t="n">
-        <v>192.1</v>
+        <v>186.4</v>
       </c>
       <c r="AJ11" t="n">
         <v>75.6844038997483</v>
       </c>
       <c r="AK11" t="n">
-        <v>25.7</v>
+        <v>26.8</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -3204,13 +3204,13 @@
         <v>-2</v>
       </c>
       <c r="I12" t="n">
-        <v>1088.2</v>
+        <v>1079.2</v>
       </c>
       <c r="J12" t="n">
         <v>1175.33</v>
       </c>
       <c r="K12" t="n">
-        <v>-7.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>69.75</v>
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2.261</v>
+        <v>2.275</v>
       </c>
       <c r="W12" t="n">
-        <v>2596</v>
+        <v>2580</v>
       </c>
       <c r="X12" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Y12" t="n">
         <v>6</v>
@@ -3280,19 +3280,19 @@
         <v>3.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1137.48</v>
+        <v>1137.12</v>
       </c>
       <c r="AH12" t="n">
-        <v>1090.23</v>
+        <v>1090.18</v>
       </c>
       <c r="AI12" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="AJ12" t="n">
         <v>1175.326204878987</v>
       </c>
       <c r="AK12" t="n">
-        <v>-7.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
@@ -3436,13 +3436,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>393.55</v>
+        <v>377.55</v>
       </c>
       <c r="J13" t="n">
         <v>217.8</v>
       </c>
       <c r="K13" t="n">
-        <v>80.7</v>
+        <v>73.3</v>
       </c>
       <c r="L13" t="n">
         <v>71.75</v>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.048</v>
+        <v>0.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1704</v>
+        <v>1651</v>
       </c>
       <c r="X13" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="Y13" t="n">
         <v>55</v>
@@ -3512,19 +3512,19 @@
         <v>14</v>
       </c>
       <c r="AG13" t="n">
-        <v>272.91</v>
+        <v>276.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>199.15</v>
+        <v>200.15</v>
       </c>
       <c r="AI13" t="n">
-        <v>166.3</v>
+        <v>154.3</v>
       </c>
       <c r="AJ13" t="n">
         <v>217.7985916238683</v>
       </c>
       <c r="AK13" t="n">
-        <v>80.7</v>
+        <v>73.3</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
@@ -3668,13 +3668,13 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>71.13</v>
+        <v>71.97</v>
       </c>
       <c r="J14" t="n">
         <v>64.48999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="L14" t="n">
         <v>64.29000000000001</v>
@@ -3711,13 +3711,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
       <c r="W14" t="n">
-        <v>862</v>
+        <v>893</v>
       </c>
       <c r="X14" t="n">
-        <v>21.8</v>
+        <v>22.6</v>
       </c>
       <c r="Y14" t="n">
         <v>19</v>
@@ -3744,17 +3744,17 @@
         <v>12.14</v>
       </c>
       <c r="AG14" t="n">
-        <v>66.26000000000001</v>
+        <v>66.42</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>40.4</v>
+        <v>42.1</v>
       </c>
       <c r="AJ14" t="n">
         <v>64.49302166476625</v>
       </c>
       <c r="AK14" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
@@ -3869,12 +3869,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VEEGALAND</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Veegaland Developers Limited</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3886,40 +3886,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>148.64</v>
+        <v>135.11</v>
       </c>
       <c r="J15" t="n">
-        <v>143.72</v>
+        <v>171.54</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>-21.2</v>
       </c>
       <c r="L15" t="n">
-        <v>63.69</v>
+        <v>74.59</v>
       </c>
       <c r="M15" t="n">
-        <v>19.68</v>
+        <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>196783125</v>
+        <v>11081344</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>196783125</v>
+        <v>11081344</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3933,58 +3933,64 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>2.783</v>
+        <v>0.065</v>
       </c>
       <c r="W15" t="n">
-        <v>707</v>
+        <v>1708</v>
       </c>
       <c r="X15" t="n">
-        <v>21.4</v>
+        <v>39.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.01</v>
+        <v>17</v>
       </c>
       <c r="AA15" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.88</v>
+        <v>0.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>14.1</v>
+        <v>30.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>17.51</v>
-      </c>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>173.55</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>474.42</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>13.9</v>
+      </c>
       <c r="AJ15" t="n">
-        <v>143.7164139971926</v>
+        <v>171.5378328173375</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.4</v>
+        <v>-21.2</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -3999,52 +4005,52 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="AR15" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="AS15" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>83720</v>
       </c>
       <c r="BA15" t="n">
-        <v>196783125</v>
+        <v>245280</v>
       </c>
       <c r="BB15" t="n">
-        <v>196783125</v>
+        <v>11081344</v>
       </c>
       <c r="BC15" t="n">
-        <v>196783125</v>
+        <v>11081344</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
@@ -4080,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>196783125</v>
+        <v>245280</v>
       </c>
       <c r="BP15" t="n">
         <v>1</v>
@@ -4095,188 +4101,182 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>VEEGALAND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>Veegaland Developers Limited</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>26</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>19</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>143.63</v>
+      </c>
+      <c r="J16" t="n">
+        <v>143.72</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>63.69</v>
+      </c>
+      <c r="M16" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="N16" t="n">
+        <v>196783125</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>196783125</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>22-09-2026</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="W16" t="n">
+        <v>699</v>
+      </c>
+      <c r="X16" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Y16" t="n">
         <v>30</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Fundamental Watch</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+      <c r="Z16" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="n">
+        <v>143.7164139971926</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>22-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ16" t="n">
         <v>4</v>
       </c>
-      <c r="F16" t="n">
-        <v>26</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>137.68</v>
-      </c>
-      <c r="J16" t="n">
-        <v>171.54</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-19.7</v>
-      </c>
-      <c r="L16" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N16" t="n">
-        <v>11081344</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>11081344</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S16" t="b">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>5</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1727</v>
-      </c>
-      <c r="X16" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>83</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>477.74</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>171.5378328173375</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>-19.7</v>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ16" t="n">
-        <v>36</v>
-      </c>
       <c r="AR16" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="AS16" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>83720</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>245280</v>
+        <v>196783125</v>
       </c>
       <c r="BB16" t="n">
-        <v>11081344</v>
+        <v>196783125</v>
       </c>
       <c r="BC16" t="n">
-        <v>11081344</v>
+        <v>196783125</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
         <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>245280</v>
+        <v>196783125</v>
       </c>
       <c r="BP16" t="n">
         <v>1</v>
@@ -4327,16 +4327,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4344,40 +4344,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F17" t="n">
-        <v>22</v>
+        <v>-5</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I17" t="n">
-        <v>73.81</v>
+        <v>57.56</v>
       </c>
       <c r="J17" t="n">
-        <v>68.68000000000001</v>
+        <v>54.07</v>
       </c>
       <c r="K17" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="L17" t="n">
-        <v>71.22</v>
+        <v>67.23</v>
       </c>
       <c r="M17" t="n">
-        <v>0.86</v>
+        <v>2.2</v>
       </c>
       <c r="N17" t="n">
-        <v>8585000</v>
+        <v>21953383</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>8585000</v>
+        <v>21953383</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -4391,54 +4391,58 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.12</v>
+        <v>1.814</v>
       </c>
       <c r="W17" t="n">
-        <v>716</v>
-      </c>
-      <c r="X17" t="n">
-        <v>31.2</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.44</v>
+        <v>2.47</v>
       </c>
       <c r="AA17" t="n">
-        <v>39</v>
+        <v>-3779</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.55</v>
+        <v>-0.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>23.9</v>
+        <v>-1.26</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AE17" t="b">
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>55.23</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.6</v>
+      </c>
       <c r="AJ17" t="n">
-        <v>68.68000000000001</v>
+        <v>54.06877621438969</v>
       </c>
       <c r="AK17" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
@@ -4447,7 +4451,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -4457,22 +4461,22 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="AS17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
@@ -4481,28 +4485,28 @@
         <v>1</v>
       </c>
       <c r="AV17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AX17" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>8585000</v>
+        <v>1828800</v>
       </c>
       <c r="BA17" t="n">
-        <v>8585000</v>
+        <v>3549124</v>
       </c>
       <c r="BB17" t="n">
-        <v>8585000</v>
+        <v>18394079</v>
       </c>
       <c r="BC17" t="n">
-        <v>8585000</v>
+        <v>21953383</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
@@ -4538,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="BO17" t="n">
-        <v>8585000</v>
+        <v>3549124</v>
       </c>
       <c r="BP17" t="n">
         <v>1</v>
@@ -4553,16 +4557,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>BERGER PAINTS (I) LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4570,40 +4574,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>-5</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>57.44</v>
+        <v>463.9</v>
       </c>
       <c r="J18" t="n">
-        <v>54.07</v>
+        <v>489.56</v>
       </c>
       <c r="K18" t="n">
-        <v>6.2</v>
+        <v>-5.2</v>
       </c>
       <c r="L18" t="n">
-        <v>67.23</v>
+        <v>75</v>
       </c>
       <c r="M18" t="n">
-        <v>2.2</v>
+        <v>4.84</v>
       </c>
       <c r="N18" t="n">
-        <v>21953383</v>
+        <v>48436318</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>21953383</v>
+        <v>48436318</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -4617,58 +4621,60 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>1.845</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>119</v>
-      </c>
-      <c r="X18" t="inlineStr"/>
+        <v>54142</v>
+      </c>
+      <c r="X18" t="n">
+        <v>45.8</v>
+      </c>
       <c r="Y18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.47</v>
+        <v>562</v>
       </c>
       <c r="AA18" t="n">
-        <v>-3779</v>
+        <v>8</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.05</v>
+        <v>3.16</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.26</v>
+        <v>22.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.8</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE18" t="b">
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="AG18" t="n">
-        <v>55.14</v>
+        <v>495.08</v>
       </c>
       <c r="AH18" t="n">
-        <v>55.24</v>
+        <v>489.09</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="AJ18" t="n">
-        <v>54.06877621438969</v>
+        <v>489.5623319654733</v>
       </c>
       <c r="AK18" t="n">
-        <v>6.2</v>
+        <v>-5.2</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -4677,62 +4683,62 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
+          <t>Mature Accumulation</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
           <t>Confirmed Accumulation</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="AS18" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AX18" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1828800</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>3549124</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>18394079</v>
+        <v>48436318</v>
       </c>
       <c r="BC18" t="n">
-        <v>21953383</v>
+        <v>48436318</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
@@ -4768,10 +4774,10 @@
         <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>3549124</v>
+        <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BQ18" t="n">
         <v>0</v>
@@ -4783,12 +4789,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BERGER PAINTS (I) LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4800,111 +4806,111 @@
         </is>
       </c>
       <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>14</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>229.66</v>
+      </c>
+      <c r="J19" t="n">
+        <v>243.52</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N19" t="n">
+        <v>11080000</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>11080000</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="F19" t="n">
-        <v>16</v>
-      </c>
-      <c r="G19" t="n">
-        <v>9</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>472.55</v>
-      </c>
-      <c r="J19" t="n">
-        <v>489.56</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="L19" t="n">
-        <v>75</v>
-      </c>
-      <c r="M19" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="N19" t="n">
-        <v>48436318</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>48436318</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S19" t="b">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.189</v>
       </c>
       <c r="W19" t="n">
-        <v>54470</v>
+        <v>586</v>
       </c>
       <c r="X19" t="n">
-        <v>46.2</v>
+        <v>49</v>
       </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="n">
-        <v>562</v>
+        <v>2.99</v>
       </c>
       <c r="AA19" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.16</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="n">
-        <v>22.9</v>
+        <v>11.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>16.21</v>
       </c>
       <c r="AG19" t="n">
-        <v>495.88</v>
+        <v>252.72</v>
       </c>
       <c r="AH19" t="n">
-        <v>489.48</v>
+        <v>191</v>
       </c>
       <c r="AI19" t="n">
-        <v>11.9</v>
+        <v>67</v>
       </c>
       <c r="AJ19" t="n">
-        <v>489.5623319654733</v>
+        <v>243.5164835164835</v>
       </c>
       <c r="AK19" t="n">
-        <v>-3.5</v>
+        <v>-5.7</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -4914,27 +4920,27 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AR19" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="AS19" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
@@ -4946,10 +4952,10 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AX19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
@@ -4961,10 +4967,10 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>48436318</v>
+        <v>4065000</v>
       </c>
       <c r="BC19" t="n">
-        <v>48436318</v>
+        <v>11080000</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
@@ -5003,7 +5009,7 @@
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BQ19" t="n">
         <v>0</v>
@@ -5015,12 +5021,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -5032,40 +5038,40 @@
         </is>
       </c>
       <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22</v>
+      </c>
+      <c r="G20" t="n">
         <v>4</v>
       </c>
-      <c r="F20" t="n">
-        <v>14</v>
-      </c>
-      <c r="G20" t="n">
-        <v>13</v>
-      </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>222.94</v>
+        <v>87.94</v>
       </c>
       <c r="J20" t="n">
-        <v>243.52</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.5</v>
+        <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>67.65000000000001</v>
+        <v>71.22</v>
       </c>
       <c r="M20" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="N20" t="n">
-        <v>11080000</v>
+        <v>8585000</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>11080000</v>
+        <v>8585000</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -5079,64 +5085,58 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.179</v>
+        <v>0.103</v>
       </c>
       <c r="W20" t="n">
-        <v>619</v>
+        <v>834</v>
       </c>
       <c r="X20" t="n">
-        <v>51.7</v>
+        <v>36.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.99</v>
+        <v>8.44</v>
       </c>
       <c r="AA20" t="n">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>11.6</v>
+        <v>23.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE20" t="b">
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>16.21</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>252.93</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>190.65</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>58.5</v>
-      </c>
+        <v>19.61</v>
+      </c>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="n">
-        <v>243.5164835164835</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="AK20" t="n">
-        <v>-8.4</v>
+        <v>28</v>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -5146,57 +5146,57 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="AS20" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW20" t="n">
         <v>1</v>
       </c>
       <c r="AX20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>8585000</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>8585000</v>
       </c>
       <c r="BB20" t="n">
-        <v>4065000</v>
+        <v>8585000</v>
       </c>
       <c r="BC20" t="n">
-        <v>11080000</v>
+        <v>8585000</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>8585000</v>
       </c>
       <c r="BP20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ20" t="n">
         <v>0</v>
@@ -5276,13 +5276,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>219.16</v>
+        <v>213</v>
       </c>
       <c r="J21" t="n">
         <v>232.74</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.8</v>
+        <v>-8.5</v>
       </c>
       <c r="L21" t="n">
         <v>67.13</v>
@@ -5322,7 +5322,7 @@
         <v>0.089</v>
       </c>
       <c r="W21" t="n">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="X21" t="n">
         <v>10.5</v>
@@ -5352,19 +5352,19 @@
         <v>9</v>
       </c>
       <c r="AG21" t="n">
-        <v>227.42</v>
+        <v>227.03</v>
       </c>
       <c r="AH21" t="n">
-        <v>205.56</v>
+        <v>205.6</v>
       </c>
       <c r="AI21" t="n">
-        <v>31.9</v>
+        <v>23.3</v>
       </c>
       <c r="AJ21" t="n">
         <v>232.7375571148825</v>
       </c>
       <c r="AK21" t="n">
-        <v>-5.8</v>
+        <v>-8.5</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -5508,13 +5508,13 @@
         <v>-1</v>
       </c>
       <c r="I22" t="n">
-        <v>575.95</v>
+        <v>568.6</v>
       </c>
       <c r="J22" t="n">
         <v>638.11</v>
       </c>
       <c r="K22" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.9</v>
       </c>
       <c r="L22" t="n">
         <v>64.68000000000001</v>
@@ -5551,13 +5551,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="W22" t="n">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="X22" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="Y22" t="n">
         <v>21</v>
@@ -5584,19 +5584,19 @@
         <v>-110</v>
       </c>
       <c r="AG22" t="n">
-        <v>593.99</v>
+        <v>594.1900000000001</v>
       </c>
       <c r="AH22" t="n">
-        <v>519.08</v>
+        <v>519.28</v>
       </c>
       <c r="AI22" t="n">
-        <v>30.4</v>
+        <v>26.4</v>
       </c>
       <c r="AJ22" t="n">
         <v>638.108361041278</v>
       </c>
       <c r="AK22" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.9</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
@@ -5740,13 +5740,13 @@
         <v>-1</v>
       </c>
       <c r="I23" t="n">
-        <v>50.37</v>
+        <v>50.11</v>
       </c>
       <c r="J23" t="n">
         <v>55.06</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.5</v>
+        <v>-9</v>
       </c>
       <c r="L23" t="n">
         <v>73.01000000000001</v>
@@ -5783,13 +5783,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.679</v>
+        <v>0.666</v>
       </c>
       <c r="W23" t="n">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="X23" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="Y23" t="n">
         <v>19</v>
@@ -5816,19 +5816,19 @@
         <v>3.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>55.31</v>
+        <v>55.12</v>
       </c>
       <c r="AH23" t="n">
-        <v>57.74</v>
+        <v>57.69</v>
       </c>
       <c r="AI23" t="n">
-        <v>-5.1</v>
+        <v>-5.5</v>
       </c>
       <c r="AJ23" t="n">
         <v>55.06464387464388</v>
       </c>
       <c r="AK23" t="n">
-        <v>-8.5</v>
+        <v>-9</v>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
@@ -5972,13 +5972,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>122.55</v>
+        <v>126.61</v>
       </c>
       <c r="J24" t="n">
         <v>132.2</v>
       </c>
       <c r="K24" t="n">
-        <v>-7.3</v>
+        <v>-4.2</v>
       </c>
       <c r="L24" t="n">
         <v>67.83</v>
@@ -6015,13 +6015,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>1.012</v>
+        <v>1.002</v>
       </c>
       <c r="W24" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="X24" t="n">
-        <v>5.73</v>
+        <v>5.8</v>
       </c>
       <c r="Y24" t="n">
         <v>31</v>
@@ -6044,19 +6044,19 @@
       </c>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="n">
-        <v>226.64</v>
+        <v>222.99</v>
       </c>
       <c r="AH24" t="n">
-        <v>265.76</v>
+        <v>265.05</v>
       </c>
       <c r="AI24" t="n">
-        <v>-49.8</v>
+        <v>-48.6</v>
       </c>
       <c r="AJ24" t="n">
         <v>132.2027333333333</v>
       </c>
       <c r="AK24" t="n">
-        <v>-7.3</v>
+        <v>-4.2</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
@@ -6171,12 +6171,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>STUDDS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>Studds Accessories Limited</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -6188,40 +6188,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G25" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>201.12</v>
+        <v>420.45</v>
       </c>
       <c r="J25" t="n">
-        <v>210.19</v>
+        <v>417.34</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.3</v>
+        <v>0.7</v>
       </c>
       <c r="L25" t="n">
-        <v>67.04000000000001</v>
+        <v>61.75</v>
       </c>
       <c r="M25" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>6171564</v>
+        <v>6931636</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>6171564</v>
+        <v>6931636</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -6235,60 +6235,60 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.347</v>
+        <v>0.042</v>
       </c>
       <c r="W25" t="n">
-        <v>178</v>
+        <v>1656</v>
       </c>
       <c r="X25" t="n">
-        <v>22.1</v>
+        <v>21.6</v>
       </c>
       <c r="Y25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
         <v>12</v>
       </c>
-      <c r="Z25" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>3.16</v>
-      </c>
       <c r="AG25" t="n">
-        <v>208.98</v>
+        <v>428.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>197.58</v>
+        <v>474.36</v>
       </c>
       <c r="AI25" t="n">
-        <v>14.7</v>
+        <v>-5.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>210.188815475785</v>
+        <v>417.3421638870492</v>
       </c>
       <c r="AK25" t="n">
-        <v>-4.3</v>
+        <v>0.7</v>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
@@ -6297,62 +6297,62 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
+          <t>Mature Accumulation</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
           <t>Confirmed Accumulation</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="AS25" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
       <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
         <v>1</v>
       </c>
-      <c r="AV25" t="n">
-        <v>7</v>
-      </c>
       <c r="AW25" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AX25" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>131838</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>3024580</v>
+        <v>6931636</v>
       </c>
       <c r="BB25" t="n">
-        <v>6171564</v>
+        <v>6931636</v>
       </c>
       <c r="BC25" t="n">
-        <v>6171564</v>
+        <v>6931636</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
@@ -6388,7 +6388,7 @@
         <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>3024580</v>
+        <v>6931636</v>
       </c>
       <c r="BP25" t="n">
         <v>1</v>
@@ -6403,16 +6403,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6420,40 +6420,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I26" t="n">
-        <v>75.93000000000001</v>
+        <v>200.4</v>
       </c>
       <c r="J26" t="n">
-        <v>81.09999999999999</v>
+        <v>210.19</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.4</v>
+        <v>-4.7</v>
       </c>
       <c r="L26" t="n">
-        <v>62.78</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>0.62</v>
       </c>
       <c r="N26" t="n">
-        <v>19959718</v>
+        <v>6171564</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>19959718</v>
+        <v>6171564</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -6467,60 +6467,60 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.52</v>
+        <v>0.323</v>
       </c>
       <c r="W26" t="n">
-        <v>384</v>
+        <v>191</v>
       </c>
       <c r="X26" t="n">
-        <v>35.7</v>
+        <v>23.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.390000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="AA26" t="n">
-        <v>-19</v>
+        <v>16</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.54</v>
+        <v>0.03</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.73</v>
+        <v>7.91</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>41.64</v>
+        <v>3.16</v>
       </c>
       <c r="AG26" t="n">
-        <v>78.04000000000001</v>
+        <v>208.91</v>
       </c>
       <c r="AH26" t="n">
-        <v>77.66</v>
+        <v>197.78</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.2</v>
+        <v>12.1</v>
       </c>
       <c r="AJ26" t="n">
-        <v>81.10277768748172</v>
+        <v>210.188815475785</v>
       </c>
       <c r="AK26" t="n">
-        <v>-6.4</v>
+        <v>-4.7</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
@@ -6539,22 +6539,22 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="AR26" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AS26" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AT26" t="n">
         <v>0</v>
@@ -6563,28 +6563,28 @@
         <v>1</v>
       </c>
       <c r="AV26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW26" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AX26" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1417187</v>
+        <v>131838</v>
       </c>
       <c r="BA26" t="n">
-        <v>5008022</v>
+        <v>3024580</v>
       </c>
       <c r="BB26" t="n">
-        <v>19959718</v>
+        <v>6171564</v>
       </c>
       <c r="BC26" t="n">
-        <v>19959718</v>
+        <v>6171564</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
@@ -6620,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="BO26" t="n">
-        <v>5008022</v>
+        <v>3024580</v>
       </c>
       <c r="BP26" t="n">
         <v>1</v>
@@ -6635,12 +6635,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -6655,37 +6655,37 @@
         <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>163.67</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>174.27</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.1</v>
+        <v>-7.4</v>
       </c>
       <c r="L27" t="n">
-        <v>61.48</v>
+        <v>62.78</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>10743104</v>
+        <v>19959718</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>10743104</v>
+        <v>19959718</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -6699,7 +6699,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -6710,49 +6710,49 @@
         <v>0.516</v>
       </c>
       <c r="W27" t="n">
-        <v>208</v>
+        <v>387</v>
       </c>
       <c r="X27" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>-44</v>
+        <v>21</v>
       </c>
       <c r="Z27" t="n">
-        <v>-3.28</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AA27" t="n">
-        <v>141</v>
+        <v>-19</v>
       </c>
       <c r="AB27" t="n">
-        <v>-4.05</v>
+        <v>1.54</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.25</v>
+        <v>8.73</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="AE27" t="b">
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>-35.96</v>
+        <v>41.64</v>
       </c>
       <c r="AG27" t="n">
-        <v>171.81</v>
+        <v>78.06</v>
       </c>
       <c r="AH27" t="n">
-        <v>177.72</v>
+        <v>77.62</v>
       </c>
       <c r="AI27" t="n">
-        <v>13.4</v>
+        <v>-1.9</v>
       </c>
       <c r="AJ27" t="n">
-        <v>174.2652478588113</v>
+        <v>81.10277768748172</v>
       </c>
       <c r="AK27" t="n">
-        <v>-6.1</v>
+        <v>-7.4</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
@@ -6780,10 +6780,10 @@
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AR27" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AS27" t="n">
         <v>13</v>
@@ -6792,31 +6792,31 @@
         <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AW27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>6755380</v>
+        <v>1417187</v>
       </c>
       <c r="BA27" t="n">
-        <v>10743104</v>
+        <v>5008022</v>
       </c>
       <c r="BB27" t="n">
-        <v>10743104</v>
+        <v>19959718</v>
       </c>
       <c r="BC27" t="n">
-        <v>10743104</v>
+        <v>19959718</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
@@ -6852,7 +6852,7 @@
         <v>0</v>
       </c>
       <c r="BO27" t="n">
-        <v>10743104</v>
+        <v>5008022</v>
       </c>
       <c r="BP27" t="n">
         <v>1</v>
@@ -6867,16 +6867,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6884,40 +6884,40 @@
         </is>
       </c>
       <c r="E28" t="n">
+        <v>11</v>
+      </c>
+      <c r="F28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
-        <v>19</v>
-      </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I28" t="n">
-        <v>145.47</v>
+        <v>165.3</v>
       </c>
       <c r="J28" t="n">
-        <v>166</v>
+        <v>174.27</v>
       </c>
       <c r="K28" t="n">
-        <v>-12.4</v>
+        <v>-5.1</v>
       </c>
       <c r="L28" t="n">
-        <v>64.08</v>
+        <v>61.48</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>8001009</v>
+        <v>10743104</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>8001009</v>
+        <v>10743104</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -6931,124 +6931,124 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.125</v>
+        <v>0.516</v>
       </c>
       <c r="W28" t="n">
-        <v>641</v>
+        <v>208</v>
       </c>
       <c r="X28" t="n">
-        <v>14.1</v>
+        <v>36</v>
       </c>
       <c r="Y28" t="n">
-        <v>-1</v>
+        <v>-44</v>
       </c>
       <c r="Z28" t="n">
-        <v>21</v>
+        <v>-3.28</v>
       </c>
       <c r="AA28" t="n">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.1</v>
+        <v>-4.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>19.3</v>
+        <v>8.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="AE28" t="b">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>11</v>
+        <v>-35.96</v>
       </c>
       <c r="AG28" t="n">
-        <v>164.73</v>
+        <v>171.43</v>
       </c>
       <c r="AH28" t="n">
-        <v>187.84</v>
+        <v>177.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>-19.3</v>
+        <v>4.2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>165.9960373443983</v>
+        <v>174.2652478588113</v>
       </c>
       <c r="AK28" t="n">
-        <v>-12.4</v>
+        <v>-5.1</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ28" t="n">
         <v>8</v>
       </c>
       <c r="AR28" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="AS28" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AW28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AX28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>6755380</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>10743104</v>
       </c>
       <c r="BB28" t="n">
-        <v>8001009</v>
+        <v>10743104</v>
       </c>
       <c r="BC28" t="n">
-        <v>8001009</v>
+        <v>10743104</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
@@ -7084,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>10743104</v>
       </c>
       <c r="BP28" t="n">
         <v>1</v>
@@ -7099,12 +7099,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -7116,171 +7116,171 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>158.87</v>
+      </c>
+      <c r="J29" t="n">
+        <v>166</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="L29" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N29" t="n">
+        <v>8001009</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>8001009</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="W29" t="n">
+        <v>642</v>
+      </c>
+      <c r="X29" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Y29" t="n">
         <v>-1</v>
       </c>
-      <c r="I29" t="n">
-        <v>25.86</v>
-      </c>
-      <c r="J29" t="n">
-        <v>27.53</v>
-      </c>
-      <c r="K29" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>61.81</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="N29" t="n">
-        <v>6470400</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>6470400</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S29" t="b">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>9</v>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="W29" t="n">
-        <v>275</v>
-      </c>
-      <c r="X29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>16</v>
-      </c>
       <c r="Z29" t="n">
-        <v>2.79</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="n">
-        <v>-30</v>
+        <v>45</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.21</v>
+        <v>3.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>18</v>
+        <v>19.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.32</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.83</v>
+        <v>11</v>
       </c>
       <c r="AG29" t="n">
-        <v>27.66</v>
+        <v>164.51</v>
       </c>
       <c r="AH29" t="n">
-        <v>31.77</v>
+        <v>187.44</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.5</v>
+        <v>-18.4</v>
       </c>
       <c r="AJ29" t="n">
-        <v>27.53361702127659</v>
+        <v>165.9960373443983</v>
       </c>
       <c r="AK29" t="n">
-        <v>-6.1</v>
+        <v>-4.3</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="AS29" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AX29" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2928900</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>4267650</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>6470400</v>
+        <v>8001009</v>
       </c>
       <c r="BC29" t="n">
-        <v>6470400</v>
+        <v>8001009</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
@@ -7316,7 +7316,7 @@
         <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>4267650</v>
+        <v>0</v>
       </c>
       <c r="BP29" t="n">
         <v>1</v>
@@ -7331,16 +7331,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STUDDS</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Studds Accessories Limited</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7348,116 +7348,116 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F30" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="J30" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="L30" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N30" t="n">
+        <v>6470400</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>6470400</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>9</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="W30" t="n">
+        <v>271</v>
+      </c>
+      <c r="X30" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="Y30" t="n">
         <v>16</v>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>407.05</v>
-      </c>
-      <c r="J30" t="n">
-        <v>417.34</v>
-      </c>
-      <c r="K30" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="L30" t="n">
-        <v>61.75</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="N30" t="n">
-        <v>6931636</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>6931636</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S30" t="b">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>11-09-2026</t>
-        </is>
-      </c>
-      <c r="V30" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1603</v>
-      </c>
-      <c r="X30" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>10</v>
-      </c>
       <c r="Z30" t="n">
-        <v>20</v>
+        <v>2.79</v>
       </c>
       <c r="AA30" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
       <c r="AB30" t="n">
-        <v>3.37</v>
+        <v>0.21</v>
       </c>
       <c r="AC30" t="n">
-        <v>23.3</v>
+        <v>18</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.01</v>
+        <v>0.32</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>12</v>
+        <v>1.83</v>
       </c>
       <c r="AG30" t="n">
-        <v>428.71</v>
+        <v>27.55</v>
       </c>
       <c r="AH30" t="n">
-        <v>474.98</v>
+        <v>31.71</v>
       </c>
       <c r="AI30" t="n">
-        <v>-9.6</v>
+        <v>2.4</v>
       </c>
       <c r="AJ30" t="n">
-        <v>417.3421638870492</v>
+        <v>27.53361702127659</v>
       </c>
       <c r="AK30" t="n">
-        <v>-2.5</v>
+        <v>-5</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
@@ -7467,52 +7467,52 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AR30" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="AS30" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AW30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AX30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>2928900</v>
       </c>
       <c r="BA30" t="n">
-        <v>6931636</v>
+        <v>4267650</v>
       </c>
       <c r="BB30" t="n">
-        <v>6931636</v>
+        <v>6470400</v>
       </c>
       <c r="BC30" t="n">
-        <v>6931636</v>
+        <v>6470400</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
@@ -7548,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>6931636</v>
+        <v>4267650</v>
       </c>
       <c r="BP30" t="n">
         <v>1</v>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7586,19 +7586,19 @@
         <v>-2</v>
       </c>
       <c r="G31" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="J31" t="n">
         <v>2.82</v>
       </c>
       <c r="K31" t="n">
-        <v>9.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="L31" t="n">
         <v>64.45</v>
@@ -7668,13 +7668,13 @@
         <v>3.17</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.3</v>
+        <v>5.6</v>
       </c>
       <c r="AJ31" t="n">
         <v>2.817550384346611</v>
       </c>
       <c r="AK31" t="n">
-        <v>9.300000000000001</v>
+        <v>14.3</v>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -7789,16 +7789,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7806,40 +7806,40 @@
         </is>
       </c>
       <c r="E32" t="n">
+        <v>7</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
         <v>9</v>
       </c>
-      <c r="F32" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G32" t="n">
-        <v>25</v>
-      </c>
       <c r="H32" t="n">
-        <v>-16</v>
+        <v>-1</v>
       </c>
       <c r="I32" t="n">
-        <v>444.35</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>349.57</v>
+        <v>96.03</v>
       </c>
       <c r="K32" t="n">
-        <v>27.1</v>
+        <v>-3.6</v>
       </c>
       <c r="L32" t="n">
-        <v>70.55</v>
+        <v>71.89</v>
       </c>
       <c r="M32" t="n">
-        <v>31.6</v>
+        <v>2.6</v>
       </c>
       <c r="N32" t="n">
-        <v>315995536</v>
+        <v>26023230</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>315995536</v>
+        <v>26023230</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -7853,124 +7853,124 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>29-09-2026</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="W32" t="n">
+        <v>941</v>
+      </c>
+      <c r="X32" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-36</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>88.94</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>100.26</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>96.02667896678967</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>29-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ32" t="n">
         <v>11</v>
       </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="V32" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="W32" t="n">
-        <v>3856</v>
-      </c>
-      <c r="X32" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>127</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>-14</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>441.84</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>433.12</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>349.5746258337085</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>05-08-2026</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ32" t="n">
-        <v>56</v>
-      </c>
       <c r="AR32" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="AS32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
       <c r="AU32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV32" t="n">
         <v>3</v>
       </c>
-      <c r="AV32" t="n">
-        <v>6</v>
-      </c>
       <c r="AW32" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AX32" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>122602303</v>
+        <v>6202680</v>
       </c>
       <c r="BA32" t="n">
-        <v>213764633</v>
+        <v>26023230</v>
       </c>
       <c r="BB32" t="n">
-        <v>262330755</v>
+        <v>26023230</v>
       </c>
       <c r="BC32" t="n">
-        <v>315995536</v>
+        <v>26023230</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
@@ -8006,7 +8006,7 @@
         <v>0</v>
       </c>
       <c r="BO32" t="n">
-        <v>213764633</v>
+        <v>26023230</v>
       </c>
       <c r="BP32" t="n">
         <v>1</v>
@@ -8021,16 +8021,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -8038,40 +8038,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H33" t="n">
         <v>-1</v>
       </c>
       <c r="I33" t="n">
-        <v>87.76000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="J33" t="n">
-        <v>96.03</v>
+        <v>12.86</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.6</v>
+        <v>-0.5</v>
       </c>
       <c r="L33" t="n">
-        <v>71.89</v>
+        <v>69.12</v>
       </c>
       <c r="M33" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="N33" t="n">
-        <v>26023230</v>
+        <v>23479616</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>26023230</v>
+        <v>23479616</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -8085,60 +8085,56 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.283</v>
+        <v>0.645</v>
       </c>
       <c r="W33" t="n">
-        <v>919</v>
+        <v>364</v>
       </c>
       <c r="X33" t="n">
-        <v>25</v>
+        <v>1174</v>
       </c>
       <c r="Y33" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>18.68</v>
-      </c>
+        <v>-61</v>
+      </c>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="n">
-        <v>-36</v>
+        <v>-98</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.85</v>
+        <v>0.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>6.83</v>
+        <v>2.46</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>4.02</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="n">
-        <v>88.91</v>
+        <v>12.68</v>
       </c>
       <c r="AH33" t="n">
-        <v>100.4</v>
+        <v>12.98</v>
       </c>
       <c r="AI33" t="n">
-        <v>5.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ33" t="n">
-        <v>96.02667896678967</v>
+        <v>12.85608234597773</v>
       </c>
       <c r="AK33" t="n">
-        <v>-8.6</v>
+        <v>-0.4</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
@@ -8157,22 +8153,22 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="AR33" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="AS33" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
@@ -8181,28 +8177,28 @@
         <v>1</v>
       </c>
       <c r="AV33" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AW33" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="AX33" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>6202680</v>
+        <v>13200</v>
       </c>
       <c r="BA33" t="n">
-        <v>26023230</v>
+        <v>6541874</v>
       </c>
       <c r="BB33" t="n">
-        <v>26023230</v>
+        <v>23479616</v>
       </c>
       <c r="BC33" t="n">
-        <v>26023230</v>
+        <v>23479616</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
@@ -8238,7 +8234,7 @@
         <v>0</v>
       </c>
       <c r="BO33" t="n">
-        <v>26023230</v>
+        <v>6541874</v>
       </c>
       <c r="BP33" t="n">
         <v>1</v>
@@ -8253,16 +8249,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -8270,107 +8266,111 @@
         </is>
       </c>
       <c r="E34" t="n">
+        <v>9</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>25</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I34" t="n">
+        <v>448.85</v>
+      </c>
+      <c r="J34" t="n">
+        <v>349.57</v>
+      </c>
+      <c r="K34" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="M34" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="N34" t="n">
+        <v>315995536</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>315995536</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
         <v>11</v>
       </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>5</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>12.55</v>
-      </c>
-      <c r="J34" t="n">
-        <v>12.86</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="L34" t="n">
-        <v>69.12</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="N34" t="n">
-        <v>23479616</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>23479616</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S34" t="b">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>25</v>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.671</v>
+        <v>0.821</v>
       </c>
       <c r="W34" t="n">
-        <v>350</v>
+        <v>3847</v>
       </c>
       <c r="X34" t="n">
-        <v>1130</v>
+        <v>26.9</v>
       </c>
       <c r="Y34" t="n">
-        <v>-61</v>
-      </c>
-      <c r="Z34" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>127</v>
+      </c>
       <c r="AA34" t="n">
-        <v>-98</v>
+        <v>-14</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.01</v>
+        <v>6.41</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.46</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.44</v>
+        <v>1.05</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>21</v>
+      </c>
       <c r="AG34" t="n">
-        <v>12.61</v>
+        <v>442.4</v>
       </c>
       <c r="AH34" t="n">
-        <v>13</v>
+        <v>433.33</v>
       </c>
       <c r="AI34" t="n">
-        <v>15.6</v>
+        <v>6.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>12.85608234597773</v>
+        <v>349.5746258337085</v>
       </c>
       <c r="AK34" t="n">
-        <v>-2.4</v>
+        <v>28.4</v>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -8380,57 +8380,57 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="AQ34" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AR34" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="AS34" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV34" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW34" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="AX34" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>13200</v>
+        <v>122602303</v>
       </c>
       <c r="BA34" t="n">
-        <v>6541874</v>
+        <v>213764633</v>
       </c>
       <c r="BB34" t="n">
-        <v>23479616</v>
+        <v>262330755</v>
       </c>
       <c r="BC34" t="n">
-        <v>23479616</v>
+        <v>315995536</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
@@ -8466,7 +8466,7 @@
         <v>0</v>
       </c>
       <c r="BO34" t="n">
-        <v>6541874</v>
+        <v>213764633</v>
       </c>
       <c r="BP34" t="n">
         <v>1</v>
@@ -8481,16 +8481,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -8501,37 +8501,37 @@
         <v>5</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>38.78</v>
+        <v>155.04</v>
       </c>
       <c r="J35" t="n">
-        <v>42.6</v>
+        <v>159.62</v>
       </c>
       <c r="K35" t="n">
-        <v>-9</v>
+        <v>-2.9</v>
       </c>
       <c r="L35" t="n">
-        <v>71.79000000000001</v>
+        <v>65.64</v>
       </c>
       <c r="M35" t="n">
-        <v>1.4</v>
+        <v>3.99</v>
       </c>
       <c r="N35" t="n">
-        <v>13998766</v>
+        <v>39906048</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>13998766</v>
+        <v>39906048</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -8545,94 +8545,94 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.365</v>
+        <v>0.232</v>
       </c>
       <c r="W35" t="n">
-        <v>384</v>
+        <v>1722</v>
       </c>
       <c r="X35" t="n">
-        <v>95.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="Y35" t="n">
-        <v>246</v>
+        <v>-3</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.91</v>
+        <v>26</v>
       </c>
       <c r="AA35" t="n">
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.14</v>
+        <v>2.36</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.07</v>
+        <v>14.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AE35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF35" t="n">
-        <v>4.21</v>
+        <v>36</v>
       </c>
       <c r="AG35" t="n">
-        <v>40.52</v>
+        <v>173.35</v>
       </c>
       <c r="AH35" t="n">
-        <v>39.78</v>
+        <v>183.81</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.5</v>
+        <v>-13.5</v>
       </c>
       <c r="AJ35" t="n">
-        <v>42.60032805144139</v>
+        <v>159.624192</v>
       </c>
       <c r="AK35" t="n">
-        <v>-9</v>
+        <v>-2.9</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="AQ35" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AR35" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="AS35" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AT35" t="n">
         <v>0</v>
@@ -8641,13 +8641,13 @@
         <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW35" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AX35" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
@@ -8656,13 +8656,13 @@
         <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>39906048</v>
       </c>
       <c r="BB35" t="n">
-        <v>13998766</v>
+        <v>39906048</v>
       </c>
       <c r="BC35" t="n">
-        <v>13998766</v>
+        <v>39906048</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
         <v>0</v>
       </c>
       <c r="BO35" t="n">
-        <v>0</v>
+        <v>39906048</v>
       </c>
       <c r="BP35" t="n">
         <v>1</v>
@@ -8713,16 +8713,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -8730,40 +8730,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>159.07</v>
+        <v>187.41</v>
       </c>
       <c r="J36" t="n">
-        <v>159.62</v>
+        <v>191.87</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.3</v>
+        <v>-2.3</v>
       </c>
       <c r="L36" t="n">
-        <v>65.64</v>
+        <v>70.02</v>
       </c>
       <c r="M36" t="n">
-        <v>3.99</v>
+        <v>1.34</v>
       </c>
       <c r="N36" t="n">
-        <v>39906048</v>
+        <v>13430794</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>39906048</v>
+        <v>13430794</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -8777,94 +8777,94 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="W36" t="n">
+        <v>3290</v>
+      </c>
+      <c r="X36" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>201.54</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>193.2</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>191.8684857142857</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Aging</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Mature Accumulation</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>Mature — Wait for Pullback</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ36" t="n">
         <v>2</v>
       </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1752</v>
-      </c>
-      <c r="X36" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>173.97</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>184.06</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>159.624192</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="AP36" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1</v>
-      </c>
       <c r="AR36" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="AS36" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AT36" t="n">
         <v>0</v>
@@ -8873,67 +8873,67 @@
         <v>0</v>
       </c>
       <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>13430794</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>13430794</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP36" t="n">
         <v>2</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO36" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="BP36" t="n">
-        <v>1</v>
       </c>
       <c r="BQ36" t="n">
         <v>0</v>
@@ -8945,57 +8945,57 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="n">
         <v>4</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
       <c r="G37" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I37" t="n">
-        <v>185.54</v>
+        <v>38.97</v>
       </c>
       <c r="J37" t="n">
-        <v>191.87</v>
+        <v>42.6</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.3</v>
+        <v>-8.5</v>
       </c>
       <c r="L37" t="n">
-        <v>70.02</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="N37" t="n">
-        <v>13430794</v>
+        <v>13998766</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>13430794</v>
+        <v>13998766</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -9009,7 +9009,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -9017,52 +9017,52 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.041</v>
+        <v>0.361</v>
       </c>
       <c r="W37" t="n">
-        <v>3275</v>
+        <v>388</v>
       </c>
       <c r="X37" t="n">
-        <v>19.4</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="Y37" t="n">
-        <v>-4</v>
+        <v>246</v>
       </c>
       <c r="Z37" t="n">
-        <v>51</v>
+        <v>0.91</v>
       </c>
       <c r="AA37" t="n">
-        <v>-9</v>
+        <v>10</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.04</v>
+        <v>0.14</v>
       </c>
       <c r="AC37" t="n">
-        <v>20.8</v>
+        <v>2.07</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>21</v>
+        <v>4.21</v>
       </c>
       <c r="AG37" t="n">
-        <v>202.16</v>
+        <v>40.51</v>
       </c>
       <c r="AH37" t="n">
-        <v>193.26</v>
+        <v>39.77</v>
       </c>
       <c r="AI37" t="n">
-        <v>10.4</v>
+        <v>-1.1</v>
       </c>
       <c r="AJ37" t="n">
-        <v>191.8684857142857</v>
+        <v>42.60032805144139</v>
       </c>
       <c r="AK37" t="n">
-        <v>-3.3</v>
+        <v>-8.5</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
@@ -9090,10 +9090,10 @@
         </is>
       </c>
       <c r="AQ37" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="AR37" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="AS37" t="n">
         <v>35</v>
@@ -9108,10 +9108,10 @@
         <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AX37" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -9123,10 +9123,10 @@
         <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>13430794</v>
+        <v>13998766</v>
       </c>
       <c r="BC37" t="n">
-        <v>13430794</v>
+        <v>13998766</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
@@ -9165,7 +9165,7 @@
         <v>0</v>
       </c>
       <c r="BP37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ37" t="n">
         <v>0</v>
@@ -9186,7 +9186,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -9206,13 +9206,13 @@
         <v>-13</v>
       </c>
       <c r="I38" t="n">
-        <v>775.5</v>
+        <v>803.8</v>
       </c>
       <c r="J38" t="n">
         <v>726.25</v>
       </c>
       <c r="K38" t="n">
-        <v>6.8</v>
+        <v>10.7</v>
       </c>
       <c r="L38" t="n">
         <v>71.92</v>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>5418</v>
+        <v>5507</v>
       </c>
       <c r="X38" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="Y38" t="n">
         <v>26</v>
@@ -9282,19 +9282,19 @@
         <v>25</v>
       </c>
       <c r="AG38" t="n">
-        <v>697.21</v>
+        <v>700.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>488.02</v>
+        <v>490.18</v>
       </c>
       <c r="AI38" t="n">
-        <v>146.5</v>
+        <v>150.9</v>
       </c>
       <c r="AJ38" t="n">
         <v>726.2520355006753</v>
       </c>
       <c r="AK38" t="n">
-        <v>6.8</v>
+        <v>10.7</v>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -9409,16 +9409,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -9429,37 +9429,37 @@
         <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G39" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>197.32</v>
+        <v>22.93</v>
       </c>
       <c r="J39" t="n">
-        <v>195.05</v>
+        <v>21.01</v>
       </c>
       <c r="K39" t="n">
-        <v>1.2</v>
+        <v>9.1</v>
       </c>
       <c r="L39" t="n">
-        <v>60.6</v>
+        <v>70.87</v>
       </c>
       <c r="M39" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="N39" t="n">
-        <v>4486152</v>
+        <v>4960333</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4486152</v>
+        <v>4960333</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -9473,122 +9473,120 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>0.011</v>
+        <v>0.114</v>
       </c>
       <c r="W39" t="n">
-        <v>4155</v>
-      </c>
-      <c r="X39" t="inlineStr"/>
+        <v>435</v>
+      </c>
+      <c r="X39" t="n">
+        <v>7.02</v>
+      </c>
       <c r="Y39" t="n">
-        <v>39</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>258</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="n">
-        <v>30</v>
+        <v>391</v>
       </c>
       <c r="AB39" t="n">
-        <v>-1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AC39" t="n">
-        <v>6.38</v>
+        <v>19.9</v>
       </c>
       <c r="AD39" t="n">
-        <v>10.11</v>
+        <v>0.01</v>
       </c>
       <c r="AE39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>61</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="n">
-        <v>189.98</v>
+        <v>20.12</v>
       </c>
       <c r="AH39" t="n">
-        <v>176.68</v>
+        <v>15.76</v>
       </c>
       <c r="AI39" t="n">
-        <v>37.6</v>
+        <v>80</v>
       </c>
       <c r="AJ39" t="n">
-        <v>195.0500869565217</v>
+        <v>21.00741139152052</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="AQ39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>51</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>49</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
         <v>3</v>
       </c>
-      <c r="AR39" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
+      <c r="AX39" t="n">
         <v>3</v>
       </c>
-      <c r="AV39" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>4</v>
-      </c>
       <c r="AY39" t="n">
         <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>3824552</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>4486152</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>4486152</v>
+        <v>4960333</v>
       </c>
       <c r="BC39" t="n">
-        <v>4486152</v>
+        <v>4960333</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
@@ -9624,7 +9622,7 @@
         <v>0</v>
       </c>
       <c r="BO39" t="n">
-        <v>4486152</v>
+        <v>0</v>
       </c>
       <c r="BP39" t="n">
         <v>1</v>
@@ -9639,16 +9637,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -9659,37 +9657,37 @@
         <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G40" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>22.95</v>
+        <v>194.57</v>
       </c>
       <c r="J40" t="n">
-        <v>21.01</v>
+        <v>195.05</v>
       </c>
       <c r="K40" t="n">
-        <v>9.199999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="L40" t="n">
-        <v>70.87</v>
+        <v>60.6</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="N40" t="n">
-        <v>4960333</v>
+        <v>4486152</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4960333</v>
+        <v>4486152</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -9703,120 +9701,122 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="W40" t="n">
+        <v>4135</v>
+      </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>258</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>190.32</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>176.68</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>195.0500869565217</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>22-09-2026</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ40" t="n">
         <v>3</v>
       </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>19-08-2026</t>
-        </is>
-      </c>
-      <c r="V40" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="W40" t="n">
-        <v>436</v>
-      </c>
-      <c r="X40" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>118</v>
-      </c>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="n">
-        <v>391</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="n">
-        <v>20.04</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>21.00741139152052</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>Aging</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="AP40" t="inlineStr">
-        <is>
-          <t>19-08-2026</t>
-        </is>
-      </c>
-      <c r="AQ40" t="n">
-        <v>2</v>
-      </c>
       <c r="AR40" t="n">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="AS40" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>3824552</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>4486152</v>
       </c>
       <c r="BB40" t="n">
-        <v>4960333</v>
+        <v>4486152</v>
       </c>
       <c r="BC40" t="n">
-        <v>4960333</v>
+        <v>4486152</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>0</v>
       </c>
       <c r="BO40" t="n">
-        <v>0</v>
+        <v>4486152</v>
       </c>
       <c r="BP40" t="n">
         <v>1</v>
@@ -9867,16 +9867,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9884,171 +9884,171 @@
         </is>
       </c>
       <c r="E41" t="n">
+        <v>7</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" t="n">
+        <v>25</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="J41" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="K41" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="L41" t="n">
+        <v>68.34</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2018403</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2018403</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>17</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>23-09-2026</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="W41" t="n">
+        <v>146</v>
+      </c>
+      <c r="X41" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>23.5472893358377</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>20-08-2026</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>23-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ41" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
         <v>1</v>
       </c>
-      <c r="F41" t="n">
-        <v>15</v>
-      </c>
-      <c r="G41" t="n">
-        <v>21</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>369.95</v>
-      </c>
-      <c r="J41" t="n">
-        <v>338.1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L41" t="n">
-        <v>66.73</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3381000</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>3381000</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S41" t="b">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>11-08-2026</t>
-        </is>
-      </c>
-      <c r="V41" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="W41" t="n">
-        <v>436</v>
-      </c>
-      <c r="X41" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>-8</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>33</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>14.36</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>369.86</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>273.91</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>338.1</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Aging</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>11-08-2026</t>
-        </is>
-      </c>
-      <c r="AP41" t="inlineStr">
-        <is>
-          <t>11-08-2026</t>
-        </is>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>57</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>57</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>0</v>
-      </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW41" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AX41" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>28656</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1351825</v>
       </c>
       <c r="BB41" t="n">
-        <v>3381000</v>
+        <v>2018403</v>
       </c>
       <c r="BC41" t="n">
-        <v>3381000</v>
+        <v>2018403</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
@@ -10084,10 +10084,10 @@
         <v>0</v>
       </c>
       <c r="BO41" t="n">
-        <v>0</v>
+        <v>1351825</v>
       </c>
       <c r="BP41" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BQ41" t="n">
         <v>0</v>
@@ -10099,16 +10099,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10116,40 +10116,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G42" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>30.06</v>
+        <v>376.4</v>
       </c>
       <c r="J42" t="n">
-        <v>23.55</v>
+        <v>338.1</v>
       </c>
       <c r="K42" t="n">
-        <v>27.6</v>
+        <v>11.3</v>
       </c>
       <c r="L42" t="n">
-        <v>68.34</v>
+        <v>66.73</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="N42" t="n">
-        <v>2018403</v>
+        <v>3381000</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2018403</v>
+        <v>3381000</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -10163,124 +10163,124 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.138</v>
+        <v>0.076</v>
       </c>
       <c r="W42" t="n">
-        <v>146</v>
+        <v>443</v>
       </c>
       <c r="X42" t="n">
-        <v>33.8</v>
+        <v>13.1</v>
       </c>
       <c r="Y42" t="n">
-        <v>19</v>
+        <v>-8</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.17</v>
+        <v>24</v>
       </c>
       <c r="AA42" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.49</v>
+        <v>14.36</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.76</v>
+        <v>9.94</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="AE42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>14.87</v>
+        <v>18</v>
       </c>
       <c r="AG42" t="n">
-        <v>24.4</v>
+        <v>370.59</v>
       </c>
       <c r="AH42" t="n">
-        <v>22.85</v>
+        <v>274.54</v>
       </c>
       <c r="AI42" t="n">
-        <v>66.2</v>
+        <v>74.3</v>
       </c>
       <c r="AJ42" t="n">
-        <v>23.5472893358377</v>
+        <v>338.1</v>
       </c>
       <c r="AK42" t="n">
-        <v>27.7</v>
+        <v>11.3</v>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AQ42" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="AS42" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
       <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
         <v>1</v>
       </c>
-      <c r="AV42" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>17</v>
-      </c>
       <c r="AX42" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>28656</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1351825</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>2018403</v>
+        <v>3381000</v>
       </c>
       <c r="BC42" t="n">
-        <v>2018403</v>
+        <v>3381000</v>
       </c>
       <c r="BD42" t="n">
         <v>0</v>
@@ -10316,10 +10316,10 @@
         <v>0</v>
       </c>
       <c r="BO42" t="n">
-        <v>1351825</v>
+        <v>0</v>
       </c>
       <c r="BP42" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BQ42" t="n">
         <v>0</v>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
@@ -10360,13 +10360,13 @@
         <v>-1</v>
       </c>
       <c r="I43" t="n">
-        <v>191.83</v>
+        <v>188.56</v>
       </c>
       <c r="J43" t="n">
         <v>170.45</v>
       </c>
       <c r="K43" t="n">
-        <v>12.5</v>
+        <v>10.6</v>
       </c>
       <c r="L43" t="n">
         <v>67.54000000000001</v>
@@ -10403,13 +10403,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="W43" t="n">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="X43" t="n">
-        <v>27.5</v>
+        <v>27.1</v>
       </c>
       <c r="Y43" t="n">
         <v>24</v>
@@ -10436,19 +10436,19 @@
         <v>2.97</v>
       </c>
       <c r="AG43" t="n">
-        <v>181.65</v>
+        <v>181.98</v>
       </c>
       <c r="AH43" t="n">
-        <v>164.47</v>
+        <v>164.59</v>
       </c>
       <c r="AI43" t="n">
-        <v>34.6</v>
+        <v>33</v>
       </c>
       <c r="AJ43" t="n">
         <v>170.4518641810919</v>
       </c>
       <c r="AK43" t="n">
-        <v>12.5</v>
+        <v>10.6</v>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
@@ -10592,13 +10592,13 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>603.2</v>
+        <v>604.55</v>
       </c>
       <c r="J44" t="n">
         <v>622.4400000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.1</v>
+        <v>-2.9</v>
       </c>
       <c r="L44" t="n">
         <v>74.02</v>
@@ -10635,10 +10635,10 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="W44" t="n">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
@@ -10666,19 +10666,19 @@
         <v>6</v>
       </c>
       <c r="AG44" t="n">
-        <v>599.27</v>
+        <v>599.37</v>
       </c>
       <c r="AH44" t="n">
-        <v>550.55</v>
+        <v>550.92</v>
       </c>
       <c r="AI44" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="AJ44" t="n">
         <v>622.4351173945973</v>
       </c>
       <c r="AK44" t="n">
-        <v>-3.1</v>
+        <v>-2.9</v>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
@@ -10822,13 +10822,13 @@
         <v>-19</v>
       </c>
       <c r="I45" t="n">
-        <v>1835.5</v>
+        <v>1854.9</v>
       </c>
       <c r="J45" t="n">
         <v>1579.83</v>
       </c>
       <c r="K45" t="n">
-        <v>16.2</v>
+        <v>17.4</v>
       </c>
       <c r="L45" t="n">
         <v>67.55</v>
@@ -10868,10 +10868,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3902</v>
+        <v>3873</v>
       </c>
       <c r="X45" t="n">
-        <v>87.8</v>
+        <v>87.2</v>
       </c>
       <c r="Y45" t="n">
         <v>42</v>
@@ -10898,19 +10898,19 @@
         <v>27</v>
       </c>
       <c r="AG45" t="n">
-        <v>1661.19</v>
+        <v>1667.14</v>
       </c>
       <c r="AH45" t="n">
-        <v>1395.06</v>
+        <v>1397.08</v>
       </c>
       <c r="AI45" t="n">
-        <v>62.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AJ45" t="n">
         <v>1579.830529039607</v>
       </c>
       <c r="AK45" t="n">
-        <v>16.2</v>
+        <v>17.4</v>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
@@ -11054,13 +11054,13 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>266.9</v>
+        <v>270.25</v>
       </c>
       <c r="J46" t="n">
         <v>278.98</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.3</v>
+        <v>-3.1</v>
       </c>
       <c r="L46" t="n">
         <v>73.72</v>
@@ -11100,10 +11100,10 @@
         <v>0.006</v>
       </c>
       <c r="W46" t="n">
-        <v>4898</v>
+        <v>4901</v>
       </c>
       <c r="X46" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="Y46" t="n">
         <v>23</v>
@@ -11126,19 +11126,19 @@
       </c>
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="n">
-        <v>296.79</v>
+        <v>295.83</v>
       </c>
       <c r="AH46" t="n">
-        <v>311.2</v>
+        <v>310.94</v>
       </c>
       <c r="AI46" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.9</v>
       </c>
       <c r="AJ46" t="n">
         <v>278.9837</v>
       </c>
       <c r="AK46" t="n">
-        <v>-4.3</v>
+        <v>-3.1</v>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
@@ -11282,13 +11282,13 @@
         <v>-18</v>
       </c>
       <c r="I47" t="n">
-        <v>1085.9</v>
+        <v>1061</v>
       </c>
       <c r="J47" t="n">
         <v>1157.18</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.2</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L47" t="n">
         <v>61.21</v>
@@ -11328,7 +11328,7 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>108435</v>
+        <v>108321</v>
       </c>
       <c r="X47" t="n">
         <v>31.2</v>
@@ -11358,19 +11358,19 @@
         <v>15</v>
       </c>
       <c r="AG47" t="n">
-        <v>1125.92</v>
+        <v>1125.82</v>
       </c>
       <c r="AH47" t="n">
-        <v>1136.72</v>
+        <v>1136.87</v>
       </c>
       <c r="AI47" t="n">
-        <v>-4.6</v>
+        <v>-6.4</v>
       </c>
       <c r="AJ47" t="n">
         <v>1157.177537688442</v>
       </c>
       <c r="AK47" t="n">
-        <v>-6.2</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
@@ -11514,13 +11514,13 @@
         <v>-1</v>
       </c>
       <c r="I48" t="n">
-        <v>108.56</v>
+        <v>106.84</v>
       </c>
       <c r="J48" t="n">
         <v>111.01</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.2</v>
+        <v>-3.8</v>
       </c>
       <c r="L48" t="n">
         <v>73.48</v>
@@ -11557,13 +11557,13 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>0.217</v>
+        <v>0.219</v>
       </c>
       <c r="W48" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="X48" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="Y48" t="n">
         <v>21</v>
@@ -11590,19 +11590,19 @@
         <v>4.11</v>
       </c>
       <c r="AG48" t="n">
-        <v>111.98</v>
+        <v>111.89</v>
       </c>
       <c r="AH48" t="n">
-        <v>117.75</v>
+        <v>117.65</v>
       </c>
       <c r="AI48" t="n">
-        <v>-0.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AJ48" t="n">
         <v>111.0077475247525</v>
       </c>
       <c r="AK48" t="n">
-        <v>-2.2</v>
+        <v>-3.8</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
@@ -11798,13 +11798,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>86.67</v>
+        <v>91.75</v>
       </c>
       <c r="D2" t="n">
         <v>77.33</v>
       </c>
       <c r="E2" t="n">
-        <v>12.1</v>
+        <v>18.6</v>
       </c>
       <c r="F2" t="n">
         <v>61.32</v>
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>835.6</v>
+        <v>824.9</v>
       </c>
       <c r="D3" t="n">
         <v>819.08</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="F3" t="n">
         <v>73</v>
@@ -11868,13 +11868,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>282.5</v>
+        <v>299.2</v>
       </c>
       <c r="D4" t="n">
         <v>265.56</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4</v>
+        <v>12.7</v>
       </c>
       <c r="F4" t="n">
         <v>64.63</v>
@@ -11894,31 +11894,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>338.55</v>
+        <v>944.4</v>
       </c>
       <c r="D5" t="n">
-        <v>333.11</v>
+        <v>869.9299999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="F5" t="n">
-        <v>63.24</v>
+        <v>61.71</v>
       </c>
       <c r="G5" t="n">
-        <v>3.75</v>
+        <v>5.19</v>
       </c>
       <c r="H5" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -11929,31 +11929,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>983.2</v>
+        <v>333.9</v>
       </c>
       <c r="D6" t="n">
-        <v>869.9299999999999</v>
+        <v>333.11</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>0.2</v>
       </c>
       <c r="F6" t="n">
-        <v>61.71</v>
+        <v>63.24</v>
       </c>
       <c r="G6" t="n">
-        <v>5.19</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -11973,13 +11973,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>548.65</v>
+        <v>549.15</v>
       </c>
       <c r="D7" t="n">
         <v>510.94</v>
       </c>
       <c r="E7" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="F7" t="n">
         <v>62.09</v>
@@ -12008,13 +12008,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>104.99</v>
+        <v>103.57</v>
       </c>
       <c r="D8" t="n">
         <v>96.81999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
         <v>70.88</v>
@@ -12043,13 +12043,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>62.86</v>
+        <v>61.19</v>
       </c>
       <c r="D9" t="n">
         <v>74.22</v>
       </c>
       <c r="E9" t="n">
-        <v>-15.3</v>
+        <v>-17.6</v>
       </c>
       <c r="F9" t="n">
         <v>72.56999999999999</v>
@@ -12078,13 +12078,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4758.5</v>
+        <v>4803</v>
       </c>
       <c r="D10" t="n">
         <v>5198.76</v>
       </c>
       <c r="E10" t="n">
-        <v>-8.5</v>
+        <v>-7.6</v>
       </c>
       <c r="F10" t="n">
         <v>67.16</v>
@@ -12113,13 +12113,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>95.09999999999999</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="D11" t="n">
         <v>75.68000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>25.7</v>
+        <v>26.8</v>
       </c>
       <c r="F11" t="n">
         <v>74.84999999999999</v>
@@ -12148,13 +12148,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1088.2</v>
+        <v>1079.2</v>
       </c>
       <c r="D12" t="n">
         <v>1175.33</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="F12" t="n">
         <v>69.75</v>
@@ -12183,13 +12183,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>393.55</v>
+        <v>377.55</v>
       </c>
       <c r="D13" t="n">
         <v>217.8</v>
       </c>
       <c r="E13" t="n">
-        <v>80.7</v>
+        <v>73.3</v>
       </c>
       <c r="F13" t="n">
         <v>71.75</v>
@@ -12218,13 +12218,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>71.13</v>
+        <v>71.97</v>
       </c>
       <c r="D14" t="n">
         <v>64.48999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="F14" t="n">
         <v>64.29000000000001</v>
@@ -12244,210 +12244,210 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VEEGALAND</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Veegaland Developers Limited</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>148.64</v>
+        <v>135.11</v>
       </c>
       <c r="D15" t="n">
-        <v>143.72</v>
+        <v>171.54</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4</v>
+        <v>-21.2</v>
       </c>
       <c r="F15" t="n">
-        <v>63.69</v>
+        <v>74.59</v>
       </c>
       <c r="G15" t="n">
-        <v>19.68</v>
+        <v>1.11</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>VEEGALAND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>Veegaland Developers Limited</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>137.68</v>
+        <v>143.63</v>
       </c>
       <c r="D16" t="n">
-        <v>171.54</v>
+        <v>143.72</v>
       </c>
       <c r="E16" t="n">
-        <v>-19.7</v>
+        <v>-0.1</v>
       </c>
       <c r="F16" t="n">
-        <v>74.59</v>
+        <v>63.69</v>
       </c>
       <c r="G16" t="n">
-        <v>1.11</v>
+        <v>19.68</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>73.81</v>
+        <v>57.56</v>
       </c>
       <c r="D17" t="n">
-        <v>68.68000000000001</v>
+        <v>54.07</v>
       </c>
       <c r="E17" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="F17" t="n">
-        <v>71.22</v>
+        <v>67.23</v>
       </c>
       <c r="G17" t="n">
-        <v>0.86</v>
+        <v>2.2</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>BERGER PAINTS (I) LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57.44</v>
+        <v>463.9</v>
       </c>
       <c r="D18" t="n">
-        <v>54.07</v>
+        <v>489.56</v>
       </c>
       <c r="E18" t="n">
-        <v>6.2</v>
+        <v>-5.2</v>
       </c>
       <c r="F18" t="n">
-        <v>67.23</v>
+        <v>75</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2</v>
+        <v>4.84</v>
       </c>
       <c r="H18" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BERGER PAINTS (I) LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>472.55</v>
+        <v>229.66</v>
       </c>
       <c r="D19" t="n">
-        <v>489.56</v>
+        <v>243.52</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.5</v>
+        <v>-5.7</v>
       </c>
       <c r="F19" t="n">
-        <v>75</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>4.84</v>
+        <v>1.11</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>222.94</v>
+        <v>87.94</v>
       </c>
       <c r="D20" t="n">
-        <v>243.52</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.5</v>
+        <v>28</v>
       </c>
       <c r="F20" t="n">
-        <v>67.65000000000001</v>
+        <v>71.22</v>
       </c>
       <c r="G20" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
@@ -12463,13 +12463,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>219.16</v>
+        <v>213</v>
       </c>
       <c r="D21" t="n">
         <v>232.74</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.8</v>
+        <v>-8.5</v>
       </c>
       <c r="F21" t="n">
         <v>67.13</v>
@@ -12498,13 +12498,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>575.95</v>
+        <v>568.6</v>
       </c>
       <c r="D22" t="n">
         <v>638.11</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.9</v>
       </c>
       <c r="F22" t="n">
         <v>64.68000000000001</v>
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>50.37</v>
+        <v>50.11</v>
       </c>
       <c r="D23" t="n">
         <v>55.06</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.5</v>
+        <v>-9</v>
       </c>
       <c r="F23" t="n">
         <v>73.01000000000001</v>
@@ -12568,13 +12568,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>122.55</v>
+        <v>126.61</v>
       </c>
       <c r="D24" t="n">
         <v>132.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.3</v>
+        <v>-4.2</v>
       </c>
       <c r="F24" t="n">
         <v>67.83</v>
@@ -12594,101 +12594,101 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>STUDDS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>Studds Accessories Limited</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>201.12</v>
+        <v>420.45</v>
       </c>
       <c r="D25" t="n">
-        <v>210.19</v>
+        <v>417.34</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3</v>
+        <v>0.7</v>
       </c>
       <c r="F25" t="n">
-        <v>67.04000000000001</v>
+        <v>61.75</v>
       </c>
       <c r="G25" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>75.93000000000001</v>
+        <v>200.4</v>
       </c>
       <c r="D26" t="n">
-        <v>81.09999999999999</v>
+        <v>210.19</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.4</v>
+        <v>-4.7</v>
       </c>
       <c r="F26" t="n">
-        <v>62.78</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0.62</v>
       </c>
       <c r="H26" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>163.67</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>174.27</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.1</v>
+        <v>-7.4</v>
       </c>
       <c r="F27" t="n">
-        <v>61.48</v>
+        <v>62.78</v>
       </c>
       <c r="G27" t="n">
-        <v>1.07</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -12699,105 +12699,105 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>145.47</v>
+        <v>165.3</v>
       </c>
       <c r="D28" t="n">
-        <v>166</v>
+        <v>174.27</v>
       </c>
       <c r="E28" t="n">
-        <v>-12.4</v>
+        <v>-5.1</v>
       </c>
       <c r="F28" t="n">
-        <v>64.08</v>
+        <v>61.48</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25.86</v>
+        <v>158.87</v>
       </c>
       <c r="D29" t="n">
-        <v>27.53</v>
+        <v>166</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.1</v>
+        <v>-4.3</v>
       </c>
       <c r="F29" t="n">
-        <v>61.81</v>
+        <v>64.08</v>
       </c>
       <c r="G29" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STUDDS</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Studds Accessories Limited</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>407.05</v>
+        <v>26.17</v>
       </c>
       <c r="D30" t="n">
-        <v>417.34</v>
+        <v>27.53</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.5</v>
+        <v>-4.9</v>
       </c>
       <c r="F30" t="n">
-        <v>61.75</v>
+        <v>61.81</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
@@ -12813,13 +12813,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="D31" t="n">
         <v>2.82</v>
       </c>
       <c r="E31" t="n">
-        <v>9.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="F31" t="n">
         <v>64.45</v>
@@ -12839,206 +12839,206 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>444.35</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>349.57</v>
+        <v>96.03</v>
       </c>
       <c r="E32" t="n">
-        <v>27.1</v>
+        <v>-3.6</v>
       </c>
       <c r="F32" t="n">
-        <v>70.55</v>
+        <v>71.89</v>
       </c>
       <c r="G32" t="n">
-        <v>31.6</v>
+        <v>2.6</v>
       </c>
       <c r="H32" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>87.76000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="D33" t="n">
-        <v>96.03</v>
+        <v>12.86</v>
       </c>
       <c r="E33" t="n">
-        <v>-8.6</v>
+        <v>-0.5</v>
       </c>
       <c r="F33" t="n">
-        <v>71.89</v>
+        <v>69.12</v>
       </c>
       <c r="G33" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>12.55</v>
+        <v>448.85</v>
       </c>
       <c r="D34" t="n">
-        <v>12.86</v>
+        <v>349.57</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.4</v>
+        <v>28.4</v>
       </c>
       <c r="F34" t="n">
-        <v>69.12</v>
+        <v>70.55</v>
       </c>
       <c r="G34" t="n">
-        <v>2.35</v>
+        <v>31.6</v>
       </c>
       <c r="H34" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38.78</v>
+        <v>155.04</v>
       </c>
       <c r="D35" t="n">
-        <v>42.6</v>
+        <v>159.62</v>
       </c>
       <c r="E35" t="n">
-        <v>-9</v>
+        <v>-2.9</v>
       </c>
       <c r="F35" t="n">
-        <v>71.79000000000001</v>
+        <v>65.64</v>
       </c>
       <c r="G35" t="n">
-        <v>1.4</v>
+        <v>3.99</v>
       </c>
       <c r="H35" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>159.07</v>
+        <v>187.41</v>
       </c>
       <c r="D36" t="n">
-        <v>159.62</v>
+        <v>191.87</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3</v>
+        <v>-2.3</v>
       </c>
       <c r="F36" t="n">
-        <v>65.64</v>
+        <v>70.02</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99</v>
+        <v>1.34</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>185.54</v>
+        <v>38.97</v>
       </c>
       <c r="D37" t="n">
-        <v>191.87</v>
+        <v>42.6</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.3</v>
+        <v>-8.5</v>
       </c>
       <c r="F37" t="n">
-        <v>70.02</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -13058,13 +13058,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>775.5</v>
+        <v>803.8</v>
       </c>
       <c r="D38" t="n">
         <v>726.25</v>
       </c>
       <c r="E38" t="n">
-        <v>6.8</v>
+        <v>10.7</v>
       </c>
       <c r="F38" t="n">
         <v>71.92</v>
@@ -13084,140 +13084,140 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>197.32</v>
+        <v>22.93</v>
       </c>
       <c r="D39" t="n">
-        <v>195.05</v>
+        <v>21.01</v>
       </c>
       <c r="E39" t="n">
-        <v>1.2</v>
+        <v>9.1</v>
       </c>
       <c r="F39" t="n">
-        <v>60.6</v>
+        <v>70.87</v>
       </c>
       <c r="G39" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>22.95</v>
+        <v>194.57</v>
       </c>
       <c r="D40" t="n">
-        <v>21.01</v>
+        <v>195.05</v>
       </c>
       <c r="E40" t="n">
-        <v>9.199999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="F40" t="n">
-        <v>70.87</v>
+        <v>60.6</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>369.95</v>
+        <v>28.56</v>
       </c>
       <c r="D41" t="n">
-        <v>338.1</v>
+        <v>23.55</v>
       </c>
       <c r="E41" t="n">
-        <v>9.4</v>
+        <v>21.3</v>
       </c>
       <c r="F41" t="n">
-        <v>66.73</v>
+        <v>68.34</v>
       </c>
       <c r="G41" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>30.06</v>
+        <v>376.4</v>
       </c>
       <c r="D42" t="n">
-        <v>23.55</v>
+        <v>338.1</v>
       </c>
       <c r="E42" t="n">
-        <v>27.6</v>
+        <v>11.3</v>
       </c>
       <c r="F42" t="n">
-        <v>68.34</v>
+        <v>66.73</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="H42" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
     </row>
@@ -13233,13 +13233,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>191.83</v>
+        <v>188.56</v>
       </c>
       <c r="D43" t="n">
         <v>170.45</v>
       </c>
       <c r="E43" t="n">
-        <v>12.5</v>
+        <v>10.6</v>
       </c>
       <c r="F43" t="n">
         <v>67.54000000000001</v>
@@ -13268,13 +13268,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>603.2</v>
+        <v>604.55</v>
       </c>
       <c r="D44" t="n">
         <v>622.4400000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>-3.1</v>
+        <v>-2.9</v>
       </c>
       <c r="F44" t="n">
         <v>74.02</v>
@@ -13303,13 +13303,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1835.5</v>
+        <v>1854.9</v>
       </c>
       <c r="D45" t="n">
         <v>1579.83</v>
       </c>
       <c r="E45" t="n">
-        <v>16.2</v>
+        <v>17.4</v>
       </c>
       <c r="F45" t="n">
         <v>67.55</v>
@@ -13338,13 +13338,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>266.9</v>
+        <v>270.25</v>
       </c>
       <c r="D46" t="n">
         <v>278.98</v>
       </c>
       <c r="E46" t="n">
-        <v>-4.3</v>
+        <v>-3.1</v>
       </c>
       <c r="F46" t="n">
         <v>73.72</v>
@@ -13373,13 +13373,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1085.9</v>
+        <v>1061</v>
       </c>
       <c r="D47" t="n">
         <v>1157.18</v>
       </c>
       <c r="E47" t="n">
-        <v>-6.2</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="F47" t="n">
         <v>61.21</v>
@@ -13408,13 +13408,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>108.56</v>
+        <v>106.84</v>
       </c>
       <c r="D48" t="n">
         <v>111.01</v>
       </c>
       <c r="E48" t="n">
-        <v>-2.2</v>
+        <v>-3.8</v>
       </c>
       <c r="F48" t="n">
         <v>73.48</v>
@@ -13464,7 +13464,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -13474,7 +13474,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -13484,7 +13484,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -13504,7 +13504,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -13514,7 +13514,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -13534,7 +13534,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
